--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>400010</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>4.49499988555908</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>4.41499996185303</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>4.46999979019165</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>268256</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>4.44500017166138</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>4.39499998092651</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>332724</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>4.3899998664856</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>208340</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>4.43499994277954</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>4.43499994277954</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>4.47499990463257</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>162330</v>
+        <v>280487</v>
       </c>
       <c r="C2715" t="n">
-        <v>4.5</v>
+        <v>4.56500005722046</v>
       </c>
       <c r="D2715" t="n">
-        <v>4.44500017166138</v>
+        <v>4.42500019073486</v>
       </c>
       <c r="E2715" t="n">
-        <v>4.48999977111816</v>
+        <v>4.53499984741211</v>
       </c>
       <c r="F2715" t="n">
-        <v>4.46500015258789</v>
+        <v>4.42500019073486</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>409857</v>
+        <v>162330</v>
       </c>
       <c r="C2716" t="n">
-        <v>4.49499988555908</v>
+        <v>4.5</v>
       </c>
       <c r="D2716" t="n">
-        <v>4.38500022888184</v>
+        <v>4.44500017166138</v>
       </c>
       <c r="E2716" t="n">
-        <v>4.49499988555908</v>
+        <v>4.48999977111816</v>
       </c>
       <c r="F2716" t="n">
-        <v>4.38500022888184</v>
+        <v>4.46500015258789</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>196142</v>
+        <v>409857</v>
       </c>
       <c r="C2717" t="n">
-        <v>4.44999980926514</v>
+        <v>4.49499988555908</v>
       </c>
       <c r="D2717" t="n">
-        <v>4.40000009536743</v>
+        <v>4.38500022888184</v>
       </c>
       <c r="E2717" t="n">
-        <v>4.40000009536743</v>
+        <v>4.49499988555908</v>
       </c>
       <c r="F2717" t="n">
-        <v>4.42000007629395</v>
+        <v>4.38500022888184</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>469217</v>
+        <v>196142</v>
       </c>
       <c r="C2718" t="n">
-        <v>4.48999977111816</v>
+        <v>4.44999980926514</v>
       </c>
       <c r="D2718" t="n">
         <v>4.40000009536743</v>
       </c>
       <c r="E2718" t="n">
-        <v>4.40999984741211</v>
+        <v>4.40000009536743</v>
       </c>
       <c r="F2718" t="n">
-        <v>4.46999979019165</v>
+        <v>4.42000007629395</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>400010</v>
+        <v>469217</v>
       </c>
       <c r="C2719" t="n">
-        <v>4.49499988555908</v>
+        <v>4.48999977111816</v>
       </c>
       <c r="D2719" t="n">
-        <v>4.41499996185303</v>
+        <v>4.40000009536743</v>
       </c>
       <c r="E2719" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="F2719" t="n">
         <v>4.46999979019165</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>4.42000007629395</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>268256</v>
+        <v>400010</v>
       </c>
       <c r="C2720" t="n">
-        <v>4.44500017166138</v>
+        <v>4.49499988555908</v>
       </c>
       <c r="D2720" t="n">
-        <v>4.39499998092651</v>
+        <v>4.41499996185303</v>
       </c>
       <c r="E2720" t="n">
-        <v>4.44000005722046</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="F2720" t="n">
-        <v>4.40000009536743</v>
+        <v>4.42000007629395</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>332724</v>
+        <v>268256</v>
       </c>
       <c r="C2721" t="n">
-        <v>4.48000001907349</v>
+        <v>4.44500017166138</v>
       </c>
       <c r="D2721" t="n">
-        <v>4.3899998664856</v>
+        <v>4.39499998092651</v>
       </c>
       <c r="E2721" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="F2721" t="n">
         <v>4.40000009536743</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>4.44000005722046</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>208340</v>
+        <v>332724</v>
       </c>
       <c r="C2722" t="n">
-        <v>4.48999977111816</v>
+        <v>4.48000001907349</v>
       </c>
       <c r="D2722" t="n">
-        <v>4.43499994277954</v>
+        <v>4.3899998664856</v>
       </c>
       <c r="E2722" t="n">
-        <v>4.43499994277954</v>
+        <v>4.40000009536743</v>
       </c>
       <c r="F2722" t="n">
-        <v>4.47499990463257</v>
+        <v>4.44000005722046</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>342836</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>4.42500019073486</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G3" t="n">
-        <v>2.79903626441956</v>
+        <v>2.79903674125671</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G5" t="n">
-        <v>2.75410056114197</v>
+        <v>2.75410079956055</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G7" t="n">
-        <v>2.65476846694946</v>
+        <v>2.6547679901123</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76119589805603</v>
+        <v>2.76119565963745</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72571992874146</v>
+        <v>2.72571969032288</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G10" t="n">
-        <v>2.65949869155884</v>
+        <v>2.65949845314026</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.58973002433777</v>
+        <v>2.58972954750061</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G12" t="n">
-        <v>2.54597640037537</v>
+        <v>2.54597616195679</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>2.54242849349976</v>
+        <v>2.54242873191833</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G14" t="n">
-        <v>2.47739005088806</v>
+        <v>2.4773895740509</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G15" t="n">
-        <v>2.49867510795593</v>
+        <v>2.49867534637451</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56371402740479</v>
+        <v>2.56371378898621</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G20" t="n">
-        <v>2.54834151268005</v>
+        <v>2.54834127426147</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G21" t="n">
-        <v>2.55188846588135</v>
+        <v>2.55188894271851</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G23" t="n">
-        <v>2.51996088027954</v>
+        <v>2.51996064186096</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G24" t="n">
-        <v>2.54242849349976</v>
+        <v>2.54242873191833</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G25" t="n">
-        <v>2.65713381767273</v>
+        <v>2.65713334083557</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>2.63111782073975</v>
+        <v>2.63111805915833</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G27" t="n">
-        <v>2.57790470123291</v>
+        <v>2.57790446281433</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G29" t="n">
-        <v>2.56134867668152</v>
+        <v>2.56134915351868</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G30" t="n">
-        <v>2.52587342262268</v>
+        <v>2.52587294578552</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G31" t="n">
-        <v>2.53769826889038</v>
+        <v>2.53769850730896</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G32" t="n">
-        <v>2.58973002433777</v>
+        <v>2.58972954750061</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G33" t="n">
-        <v>2.60273694992065</v>
+        <v>2.60273718833923</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>2.63111782073975</v>
+        <v>2.63111805915833</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76710796356201</v>
+        <v>2.76710820198059</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G39" t="n">
-        <v>2.79075860977173</v>
+        <v>2.79075884819031</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G40" t="n">
-        <v>2.79075860977173</v>
+        <v>2.79075884819031</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>2.73754525184631</v>
+        <v>2.73754549026489</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G42" t="n">
-        <v>2.73045039176941</v>
+        <v>2.73045015335083</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79194140434265</v>
+        <v>2.79194164276123</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77893352508545</v>
+        <v>2.77893376350403</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G46" t="n">
-        <v>2.79903626441956</v>
+        <v>2.79903674125671</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G48" t="n">
-        <v>2.73399758338928</v>
+        <v>2.7339973449707</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>2.70798206329346</v>
+        <v>2.70798254013062</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G50" t="n">
-        <v>2.67132377624512</v>
+        <v>2.67132353782654</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G51" t="n">
-        <v>2.76829123497009</v>
+        <v>2.76829099655151</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G53" t="n">
-        <v>2.73399758338928</v>
+        <v>2.7339973449707</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>2.78484630584717</v>
+        <v>2.78484582901001</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G55" t="n">
-        <v>2.72690224647522</v>
+        <v>2.72690272331238</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.75</v>
       </c>
       <c r="G56" t="n">
-        <v>2.80849695205688</v>
+        <v>2.80849671363831</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G57" t="n">
-        <v>2.8061318397522</v>
+        <v>2.80613207817078</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>2.80258417129517</v>
+        <v>2.80258369445801</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G59" t="n">
-        <v>2.78839373588562</v>
+        <v>2.7883939743042</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>2.77893352508545</v>
+        <v>2.77893376350403</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>2.78484630584717</v>
+        <v>2.78484582901001</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.75</v>
       </c>
       <c r="G62" t="n">
-        <v>2.80849695205688</v>
+        <v>2.80849671363831</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G63" t="n">
-        <v>2.79075860977173</v>
+        <v>2.79075884819031</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G64" t="n">
-        <v>2.80258417129517</v>
+        <v>2.80258369445801</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G65" t="n">
-        <v>2.76119589805603</v>
+        <v>2.76119565963745</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.63399982452393</v>
       </c>
       <c r="G67" t="n">
-        <v>2.73991012573242</v>
+        <v>2.73990988731384</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G68" t="n">
-        <v>2.67723631858826</v>
+        <v>2.67723655700684</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.66068077087402</v>
+        <v>2.66068124771118</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G70" t="n">
-        <v>2.78721117973328</v>
+        <v>2.78721165657043</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>2.76710796356201</v>
+        <v>2.76710820198059</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G73" t="n">
-        <v>2.72571992874146</v>
+        <v>2.72571969032288</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G74" t="n">
-        <v>2.71862459182739</v>
+        <v>2.71862506866455</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G76" t="n">
-        <v>2.66777634620667</v>
+        <v>2.66777658462524</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G77" t="n">
-        <v>2.59564232826233</v>
+        <v>2.59564208984375</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>2.56016659736633</v>
+        <v>2.56016635894775</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G79" t="n">
-        <v>2.49985790252686</v>
+        <v>2.49985766410828</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>2.60155463218689</v>
+        <v>2.60155415534973</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>2.64885568618774</v>
+        <v>2.6488561630249</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G87" t="n">
-        <v>2.63821339607239</v>
+        <v>2.63821315765381</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>2.57790470123291</v>
+        <v>2.57790446281433</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>2.60155463218689</v>
+        <v>2.60155415534973</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G93" t="n">
-        <v>2.54242849349976</v>
+        <v>2.54242873191833</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G95" t="n">
-        <v>2.50458812713623</v>
+        <v>2.50458765029907</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G96" t="n">
-        <v>2.54006314277649</v>
+        <v>2.54006338119507</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G97" t="n">
-        <v>2.54242849349976</v>
+        <v>2.54242873191833</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G100" t="n">
-        <v>2.59212756156921</v>
+        <v>2.59212779998779</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>2.58601450920105</v>
+        <v>2.58601403236389</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G105" t="n">
-        <v>2.61535859107971</v>
+        <v>2.61535882949829</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G108" t="n">
-        <v>2.5970184803009</v>
+        <v>2.59701871871948</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>2.5676736831665</v>
+        <v>2.56767392158508</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>2.50653862953186</v>
+        <v>2.50653839111328</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G117" t="n">
-        <v>2.37204194068909</v>
+        <v>2.37204170227051</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.26199865341187</v>
+        <v>2.26199841499329</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G119" t="n">
-        <v>2.31090617179871</v>
+        <v>2.31090641021729</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G122" t="n">
-        <v>2.33902883529663</v>
+        <v>2.33902859687805</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G124" t="n">
-        <v>2.24732613563538</v>
+        <v>2.2473258972168</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.44400000572205</v>
       </c>
       <c r="G125" t="n">
-        <v>2.10549235343933</v>
+        <v>2.10549259185791</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.75</v>
       </c>
       <c r="G126" t="n">
-        <v>2.2925660610199</v>
+        <v>2.29256582260132</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G128" t="n">
-        <v>2.47597146034241</v>
+        <v>2.47597122192383</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G135" t="n">
-        <v>2.49431157112122</v>
+        <v>2.49431180953979</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>2.54321980476379</v>
+        <v>2.54321956634521</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G138" t="n">
-        <v>2.50898408889771</v>
+        <v>2.50898385047913</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G139" t="n">
-        <v>2.50898408889771</v>
+        <v>2.50898385047913</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G140" t="n">
-        <v>2.54321980476379</v>
+        <v>2.54321956634521</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="n">
-        <v>2.50531578063965</v>
+        <v>2.50531601905823</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G143" t="n">
-        <v>2.5028703212738</v>
+        <v>2.50287079811096</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G145" t="n">
-        <v>2.47597146034241</v>
+        <v>2.47597122192383</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>2.47597146034241</v>
+        <v>2.47597122192383</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>2.5676736831665</v>
+        <v>2.56767392158508</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G148" t="n">
-        <v>2.54933285713196</v>
+        <v>2.54933333396912</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>2.54321980476379</v>
+        <v>2.54321956634521</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G150" t="n">
-        <v>2.54933285713196</v>
+        <v>2.54933333396912</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G151" t="n">
-        <v>2.48942112922668</v>
+        <v>2.48942089080811</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G152" t="n">
-        <v>2.53588318824768</v>
+        <v>2.53588342666626</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G154" t="n">
-        <v>2.50653862953186</v>
+        <v>2.50653839111328</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.45273995399475</v>
+        <v>2.45273971557617</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G163" t="n">
-        <v>2.4001636505127</v>
+        <v>2.40016388893127</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G166" t="n">
-        <v>2.35492396354675</v>
+        <v>2.35492372512817</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G168" t="n">
-        <v>2.29867935180664</v>
+        <v>2.29867959022522</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>2.34758734703064</v>
+        <v>2.34758758544922</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G172" t="n">
-        <v>2.33536076545715</v>
+        <v>2.33536052703857</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>2.35370111465454</v>
+        <v>2.35370087623596</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G177" t="n">
-        <v>2.3708188533783</v>
+        <v>2.37081861495972</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G179" t="n">
-        <v>2.2827844619751</v>
+        <v>2.28278422355652</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G181" t="n">
-        <v>2.21309041976929</v>
+        <v>2.21309018135071</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="n">
-        <v>2.18619060516357</v>
+        <v>2.18619108200073</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G183" t="n">
-        <v>2.19108152389526</v>
+        <v>2.19108128547668</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21309041976929</v>
+        <v>2.21309018135071</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G186" t="n">
-        <v>2.21309041976929</v>
+        <v>2.21309018135071</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G187" t="n">
-        <v>2.27422523498535</v>
+        <v>2.27422547340393</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G190" t="n">
-        <v>2.2020857334137</v>
+        <v>2.20208597183228</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G194" t="n">
-        <v>2.28033900260925</v>
+        <v>2.28033876419067</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>2.17029571533203</v>
+        <v>2.17029547691345</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.17029571533203</v>
+        <v>2.17029547691345</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>2.12138795852661</v>
+        <v>2.12138772010803</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G203" t="n">
-        <v>2.16418194770813</v>
+        <v>2.16418218612671</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G204" t="n">
-        <v>2.15440058708191</v>
+        <v>2.15440034866333</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G205" t="n">
-        <v>2.18374514579773</v>
+        <v>2.18374538421631</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>2.17029571533203</v>
+        <v>2.17029547691345</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>2.17029571533203</v>
+        <v>2.17029547691345</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G212" t="n">
-        <v>2.17029571533203</v>
+        <v>2.17029547691345</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>2.17029571533203</v>
+        <v>2.17029547691345</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.17029571533203</v>
+        <v>2.17029547691345</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G215" t="n">
-        <v>2.12505555152893</v>
+        <v>2.12505578994751</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>2.0908203125</v>
+        <v>2.09082007408142</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G218" t="n">
-        <v>2.0908203125</v>
+        <v>2.09082007408142</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>2.07859325408936</v>
+        <v>2.07859301567078</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G224" t="n">
-        <v>1.94531857967377</v>
+        <v>1.94531881809235</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G225" t="n">
-        <v>1.90863716602325</v>
+        <v>1.90863764286041</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>1.88296055793762</v>
+        <v>1.8829607963562</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G227" t="n">
-        <v>1.91230571269989</v>
+        <v>1.91230547428131</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G231" t="n">
-        <v>1.88418340682983</v>
+        <v>1.88418352603912</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.8523930311203</v>
+        <v>1.85239326953888</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G233" t="n">
-        <v>1.84383428096771</v>
+        <v>1.84383463859558</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G234" t="n">
-        <v>1.80837619304657</v>
+        <v>1.80837547779083</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G235" t="n">
-        <v>1.86584305763245</v>
+        <v>1.86584293842316</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G237" t="n">
-        <v>1.86217474937439</v>
+        <v>1.86217498779297</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G239" t="n">
-        <v>1.8523930311203</v>
+        <v>1.85239326953888</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G240" t="n">
-        <v>1.93186867237091</v>
+        <v>1.93186891078949</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G241" t="n">
-        <v>1.92697787284851</v>
+        <v>1.92697763442993</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G243" t="n">
-        <v>1.91964221000671</v>
+        <v>1.91964197158813</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G244" t="n">
-        <v>1.93309140205383</v>
+        <v>1.93309164047241</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G245" t="n">
-        <v>1.94898653030396</v>
+        <v>1.94898676872253</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G247" t="n">
-        <v>2.01745772361755</v>
+        <v>2.01745820045471</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G248" t="n">
-        <v>2.10426950454712</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>2.14584159851074</v>
+        <v>2.14584183692932</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>2.16418194770813</v>
+        <v>2.16418218612671</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G254" t="n">
-        <v>2.17029571533203</v>
+        <v>2.17029547691345</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G255" t="n">
-        <v>2.17640924453735</v>
+        <v>2.17640948295593</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G259" t="n">
-        <v>2.23754453659058</v>
+        <v>2.237544298172</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24243545532227</v>
+        <v>2.24243497848511</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G265" t="n">
-        <v>2.21309041976929</v>
+        <v>2.21309018135071</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G267" t="n">
-        <v>2.25588488578796</v>
+        <v>2.25588512420654</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G273" t="n">
-        <v>2.41116809844971</v>
+        <v>2.41116833686829</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31701993942261</v>
+        <v>2.31701946258545</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G278" t="n">
-        <v>2.26322078704834</v>
+        <v>2.26322102546692</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28033900260925</v>
+        <v>2.28033876419067</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G281" t="n">
-        <v>2.26322078704834</v>
+        <v>2.26322102546692</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G282" t="n">
-        <v>2.29867935180664</v>
+        <v>2.29867959022522</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G283" t="n">
-        <v>2.29867935180664</v>
+        <v>2.29867959022522</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G284" t="n">
-        <v>2.31824254989624</v>
+        <v>2.31824278831482</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G285" t="n">
-        <v>2.55300116539001</v>
+        <v>2.55300140380859</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.54933285713196</v>
+        <v>2.54933333396912</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G290" t="n">
-        <v>2.61535859107971</v>
+        <v>2.61535882949829</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G292" t="n">
-        <v>2.62758612632751</v>
+        <v>2.62758636474609</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G293" t="n">
-        <v>2.6129138469696</v>
+        <v>2.61291360855103</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>2.5676736831665</v>
+        <v>2.56767392158508</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>2.64714980125427</v>
+        <v>2.64714932441711</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G300" t="n">
-        <v>2.66548991203308</v>
+        <v>2.66549015045166</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G301" t="n">
-        <v>2.64837217330933</v>
+        <v>2.64837193489075</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>2.87334895133972</v>
+        <v>2.8733491897583</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G307" t="n">
-        <v>2.75596976280212</v>
+        <v>2.7559700012207</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G308" t="n">
-        <v>2.68872094154358</v>
+        <v>2.68872117996216</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G309" t="n">
-        <v>2.7205114364624</v>
+        <v>2.72051167488098</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.71439814567566</v>
+        <v>2.71439790725708</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G311" t="n">
-        <v>2.83422303199768</v>
+        <v>2.8342227935791</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G312" t="n">
-        <v>2.89413475990295</v>
+        <v>2.89413571357727</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G313" t="n">
-        <v>2.938152551651</v>
+        <v>2.93815231323242</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>2.94304323196411</v>
+        <v>2.94304299354553</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>2.93448400497437</v>
+        <v>2.93448424339294</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G316" t="n">
-        <v>2.94671177864075</v>
+        <v>2.94671130180359</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G317" t="n">
-        <v>2.88679885864258</v>
+        <v>2.88679909706116</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G319" t="n">
-        <v>2.90636229515076</v>
+        <v>2.90636205673218</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.92837119102478</v>
+        <v>2.92837023735046</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G321" t="n">
-        <v>2.95037961006165</v>
+        <v>2.95037937164307</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G322" t="n">
-        <v>2.98339223861694</v>
+        <v>2.9833927154541</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G324" t="n">
-        <v>2.93203902244568</v>
+        <v>2.93203949928284</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.92837119102478</v>
+        <v>2.92837023735046</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G329" t="n">
-        <v>2.90636229515076</v>
+        <v>2.90636205673218</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G331" t="n">
-        <v>2.86234521865845</v>
+        <v>2.86234498023987</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G332" t="n">
-        <v>2.90147137641907</v>
+        <v>2.90147161483765</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G335" t="n">
-        <v>2.80610060691833</v>
+        <v>2.80610108375549</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G336" t="n">
-        <v>2.79142785072327</v>
+        <v>2.79142761230469</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>2.85500860214233</v>
+        <v>2.85500884056091</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G338" t="n">
-        <v>2.93448400497437</v>
+        <v>2.93448424339294</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G339" t="n">
-        <v>2.93692970275879</v>
+        <v>2.93692898750305</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G340" t="n">
-        <v>2.94793438911438</v>
+        <v>2.9479341506958</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G342" t="n">
-        <v>2.97238802909851</v>
+        <v>2.97238826751709</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G343" t="n">
-        <v>2.94671177864075</v>
+        <v>2.94671130180359</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G344" t="n">
-        <v>2.93326163291931</v>
+        <v>2.93326187133789</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G345" t="n">
-        <v>2.92592549324036</v>
+        <v>2.92592525482178</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G346" t="n">
-        <v>3.04330444335938</v>
+        <v>3.04330492019653</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>3.04452729225159</v>
+        <v>3.04452705383301</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>3.03841376304626</v>
+        <v>3.03841400146484</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>2.87334895133972</v>
+        <v>2.8733491897583</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G353" t="n">
-        <v>2.88557600975037</v>
+        <v>2.88557624816895</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G354" t="n">
-        <v>2.88068509101868</v>
+        <v>2.88068532943726</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G355" t="n">
-        <v>2.90071868896484</v>
+        <v>2.900719165802</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G357" t="n">
-        <v>2.83878612518311</v>
+        <v>2.83878636360168</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G358" t="n">
-        <v>2.89313530921936</v>
+        <v>2.89313507080078</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G363" t="n">
-        <v>2.90703797340393</v>
+        <v>2.90703868865967</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G365" t="n">
-        <v>2.8830235004425</v>
+        <v>2.88302326202393</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G366" t="n">
-        <v>2.91462159156799</v>
+        <v>2.91462182998657</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>2.93863654136658</v>
+        <v>2.93863677978516</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G371" t="n">
-        <v>2.91588544845581</v>
+        <v>2.91588616371155</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G372" t="n">
-        <v>2.96391534805298</v>
+        <v>2.9639151096344</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>2.95759510993958</v>
+        <v>2.95759582519531</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96012353897095</v>
+        <v>2.96012306213379</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G376" t="n">
-        <v>2.99172139167786</v>
+        <v>2.99172186851501</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G379" t="n">
-        <v>2.96897077560425</v>
+        <v>2.96897101402283</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G380" t="n">
-        <v>2.91335821151733</v>
+        <v>2.9133574962616</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G381" t="n">
-        <v>2.90071868896484</v>
+        <v>2.900719165802</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G383" t="n">
-        <v>2.78317284584045</v>
+        <v>2.78317308425903</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G384" t="n">
-        <v>2.75915837287903</v>
+        <v>2.75915861129761</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G385" t="n">
-        <v>2.70354557037354</v>
+        <v>2.70354533195496</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G390" t="n">
-        <v>2.79834008216858</v>
+        <v>2.79834032058716</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G393" t="n">
-        <v>2.88175988197327</v>
+        <v>2.88175964355469</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>2.87544012069702</v>
+        <v>2.8754403591156</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G395" t="n">
-        <v>2.85774517059326</v>
+        <v>2.85774493217468</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G396" t="n">
-        <v>2.84637022018433</v>
+        <v>2.84636974334717</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G398" t="n">
-        <v>2.90071868896484</v>
+        <v>2.900719165802</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G400" t="n">
-        <v>2.90071868896484</v>
+        <v>2.900719165802</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.65199995040894</v>
       </c>
       <c r="G405" t="n">
-        <v>2.93990015983582</v>
+        <v>2.93990039825439</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.80600023269653</v>
       </c>
       <c r="G406" t="n">
-        <v>3.03722333908081</v>
+        <v>3.03722286224365</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G407" t="n">
-        <v>3.00941705703735</v>
+        <v>3.0094165802002</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.0144727230072</v>
+        <v>3.01447224617004</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G410" t="n">
-        <v>3.00309658050537</v>
+        <v>3.00309634208679</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>3.02711176872253</v>
+        <v>3.02711129188538</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>2.9828736782074</v>
+        <v>2.98287415504456</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>2.90703797340393</v>
+        <v>2.90703868865967</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G415" t="n">
-        <v>2.96391534805298</v>
+        <v>2.9639151096344</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G416" t="n">
-        <v>2.97023463249207</v>
+        <v>2.97023487091064</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G417" t="n">
-        <v>2.99298524856567</v>
+        <v>2.99298548698425</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G418" t="n">
-        <v>2.94369220733643</v>
+        <v>2.943692445755</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>2.94495630264282</v>
+        <v>2.94495606422424</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G421" t="n">
-        <v>2.87670421600342</v>
+        <v>2.87670373916626</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G423" t="n">
-        <v>2.89945411682129</v>
+        <v>2.89945435523987</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G427" t="n">
-        <v>2.90703797340393</v>
+        <v>2.90703868865967</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G428" t="n">
-        <v>2.93358111381531</v>
+        <v>2.93358063697815</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>2.90703797340393</v>
+        <v>2.90703868865967</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G432" t="n">
-        <v>2.93863654136658</v>
+        <v>2.93863677978516</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G433" t="n">
-        <v>2.98034596443176</v>
+        <v>2.9803466796875</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G436" t="n">
-        <v>3.00309658050537</v>
+        <v>3.00309634208679</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.97655439376831</v>
+        <v>2.97655463218689</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G438" t="n">
-        <v>2.96391534805298</v>
+        <v>2.9639151096344</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>2.96897077560425</v>
+        <v>2.96897101402283</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G442" t="n">
-        <v>2.95380330085754</v>
+        <v>2.95380353927612</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G443" t="n">
-        <v>2.97655439376831</v>
+        <v>2.97655463218689</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G444" t="n">
-        <v>2.97402667999268</v>
+        <v>2.9740264415741</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.65199995040894</v>
       </c>
       <c r="G449" t="n">
-        <v>2.93990015983582</v>
+        <v>2.93990039825439</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94369220733643</v>
+        <v>2.943692445755</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>3.15982413291931</v>
+        <v>3.15982389450073</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>3.19142270088196</v>
+        <v>3.19142246246338</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G457" t="n">
-        <v>3.22618007659912</v>
+        <v>3.22618079185486</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G458" t="n">
-        <v>3.12443447113037</v>
+        <v>3.12443399429321</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G460" t="n">
-        <v>3.16614437103271</v>
+        <v>3.16614389419556</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G463" t="n">
-        <v>3.38101196289062</v>
+        <v>3.38101172447205</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.25</v>
       </c>
       <c r="G464" t="n">
-        <v>3.31781578063965</v>
+        <v>3.31781530380249</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.25</v>
       </c>
       <c r="G465" t="n">
-        <v>3.31781578063965</v>
+        <v>3.31781530380249</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>3.30517601966858</v>
+        <v>3.30517554283142</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G467" t="n">
-        <v>3.34309434890747</v>
+        <v>3.34309339523315</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G469" t="n">
-        <v>3.30833601951599</v>
+        <v>3.30833625793457</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>3.28937673568726</v>
+        <v>3.28937697410583</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G471" t="n">
-        <v>3.31465530395508</v>
+        <v>3.31465601921082</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>3.27989768981934</v>
+        <v>3.27989745140076</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>3.24198031425476</v>
+        <v>3.2419798374176</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G478" t="n">
-        <v>3.20406198501587</v>
+        <v>3.20406222343445</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G480" t="n">
-        <v>3.1042115688324</v>
+        <v>3.10421109199524</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>3.13454556465149</v>
+        <v>3.13454580307007</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G483" t="n">
-        <v>3.17562317848206</v>
+        <v>3.17562365531921</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G484" t="n">
-        <v>3.23250031471252</v>
+        <v>3.23250007629395</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G485" t="n">
-        <v>3.27989768981934</v>
+        <v>3.27989745140076</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G486" t="n">
-        <v>3.30201601982117</v>
+        <v>3.30201649665833</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G487" t="n">
-        <v>3.30201601982117</v>
+        <v>3.30201649665833</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G488" t="n">
-        <v>3.25777864456177</v>
+        <v>3.25777888298035</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G489" t="n">
-        <v>3.30833601951599</v>
+        <v>3.30833625793457</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G490" t="n">
-        <v>3.35573387145996</v>
+        <v>3.3557333946228</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G492" t="n">
-        <v>3.36837244033813</v>
+        <v>3.36837267875671</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G493" t="n">
-        <v>3.41576933860779</v>
+        <v>3.41576981544495</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G495" t="n">
-        <v>3.39365100860596</v>
+        <v>3.39365077018738</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>3.36837244033813</v>
+        <v>3.36837267875671</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.375</v>
       </c>
       <c r="G497" t="n">
-        <v>3.39681124687195</v>
+        <v>3.39681100845337</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>3.43156909942627</v>
+        <v>3.43156886100769</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G500" t="n">
-        <v>3.35573387145996</v>
+        <v>3.3557333946228</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>3.24198031425476</v>
+        <v>3.2419798374176</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>3.21354103088379</v>
+        <v>3.21354079246521</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>3.21354103088379</v>
+        <v>3.21354079246521</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G506" t="n">
-        <v>3.20406198501587</v>
+        <v>3.20406222343445</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>3.19142270088196</v>
+        <v>3.19142246246338</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G509" t="n">
-        <v>3.17246341705322</v>
+        <v>3.17246317863464</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>3.20722198486328</v>
+        <v>3.20722126960754</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G513" t="n">
-        <v>3.29885625839233</v>
+        <v>3.29885649681091</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.25</v>
       </c>
       <c r="G514" t="n">
-        <v>3.31781578063965</v>
+        <v>3.31781530380249</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>3.34941363334656</v>
+        <v>3.34941387176514</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G516" t="n">
-        <v>3.34941363334656</v>
+        <v>3.34941387176514</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>3.31149506568909</v>
+        <v>3.31149530410767</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>3.33677411079407</v>
+        <v>3.33677458763123</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G522" t="n">
-        <v>3.24829888343811</v>
+        <v>3.24829936027527</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>3.22302079200745</v>
+        <v>3.22302055358887</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G524" t="n">
-        <v>3.19142270088196</v>
+        <v>3.19142246246338</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G526" t="n">
-        <v>3.34941363334656</v>
+        <v>3.34941387176514</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G527" t="n">
-        <v>3.24829888343811</v>
+        <v>3.24829936027527</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G528" t="n">
-        <v>3.27989768981934</v>
+        <v>3.27989745140076</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G529" t="n">
-        <v>3.24198031425476</v>
+        <v>3.2419798374176</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G530" t="n">
-        <v>3.19774222373962</v>
+        <v>3.19774198532104</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.875</v>
       </c>
       <c r="G532" t="n">
-        <v>3.08082866668701</v>
+        <v>3.08082890510559</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>3.121906042099</v>
+        <v>3.12190651893616</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>3.13138580322266</v>
+        <v>3.13138628005981</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.75</v>
       </c>
       <c r="G536" t="n">
-        <v>3.00183320045471</v>
+        <v>3.00183272361755</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.93863654136658</v>
+        <v>2.93863677978516</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G539" t="n">
-        <v>2.93231725692749</v>
+        <v>2.93231678009033</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G543" t="n">
-        <v>2.85964107513428</v>
+        <v>2.85964131355286</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.87228012084961</v>
+        <v>2.87227988243103</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G545" t="n">
-        <v>2.99867296218872</v>
+        <v>2.99867343902588</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G546" t="n">
-        <v>2.96075534820557</v>
+        <v>2.96075487136841</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G548" t="n">
-        <v>2.91335821151733</v>
+        <v>2.9133574962616</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90387845039368</v>
+        <v>2.90387797355652</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G551" t="n">
-        <v>2.98603367805481</v>
+        <v>2.98603343963623</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G556" t="n">
-        <v>2.83752202987671</v>
+        <v>2.83752155303955</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G557" t="n">
-        <v>2.93231725692749</v>
+        <v>2.93231678009033</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.625</v>
       </c>
       <c r="G559" t="n">
-        <v>2.92283725738525</v>
+        <v>2.92283749580383</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G560" t="n">
-        <v>2.9544358253479</v>
+        <v>2.95443534851074</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>2.97023463249207</v>
+        <v>2.97023487091064</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G562" t="n">
-        <v>2.9828736782074</v>
+        <v>2.98287415504456</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.625</v>
       </c>
       <c r="G563" t="n">
-        <v>2.92283725738525</v>
+        <v>2.92283749580383</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90703797340393</v>
+        <v>2.90703868865967</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G565" t="n">
-        <v>2.8943989276886</v>
+        <v>2.89439940452576</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G567" t="n">
-        <v>2.90703797340393</v>
+        <v>2.90703868865967</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G568" t="n">
-        <v>2.95759510993958</v>
+        <v>2.95759582519531</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G569" t="n">
-        <v>2.88175988197327</v>
+        <v>2.88175964355469</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>2.93863654136658</v>
+        <v>2.93863677978516</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G572" t="n">
-        <v>2.90071868896484</v>
+        <v>2.900719165802</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>2.80908370018005</v>
+        <v>2.80908393859863</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>2.88491988182068</v>
+        <v>2.8849196434021</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G581" t="n">
-        <v>2.88175988197327</v>
+        <v>2.88175964355469</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G582" t="n">
-        <v>2.88175988197327</v>
+        <v>2.88175964355469</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>2.86596035957336</v>
+        <v>2.86596059799194</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>2.87544012069702</v>
+        <v>2.8754403591156</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>2.8943989276886</v>
+        <v>2.89439940452576</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>2.93863654136658</v>
+        <v>2.93863677978516</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>2.97023463249207</v>
+        <v>2.97023487091064</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G592" t="n">
-        <v>3.00499296188354</v>
+        <v>3.00499320030212</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G594" t="n">
-        <v>2.95759510993958</v>
+        <v>2.95759582519531</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>2.97023463249207</v>
+        <v>2.97023487091064</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G596" t="n">
-        <v>2.9828736782074</v>
+        <v>2.98287415504456</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G600" t="n">
-        <v>3.02395153045654</v>
+        <v>3.02395176887512</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>2.97023463249207</v>
+        <v>2.97023487091064</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>2.97023463249207</v>
+        <v>2.97023487091064</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>2.97023463249207</v>
+        <v>2.97023487091064</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>2.94495630264282</v>
+        <v>2.94495606422424</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>2.73008823394775</v>
+        <v>2.73008871078491</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>2.74175810813904</v>
+        <v>2.74175786972046</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>2.80474901199341</v>
+        <v>2.80474877357483</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G615" t="n">
-        <v>2.74507308006287</v>
+        <v>2.74507331848145</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76496481895447</v>
+        <v>2.76496529579163</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G617" t="n">
-        <v>2.85447812080383</v>
+        <v>2.85447835922241</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>2.93073034286499</v>
+        <v>2.93073081970215</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G620" t="n">
-        <v>2.96388292312622</v>
+        <v>2.96388339996338</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G621" t="n">
-        <v>2.91083836555481</v>
+        <v>2.91083860397339</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.80474901199341</v>
+        <v>2.80474877357483</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G623" t="n">
-        <v>2.89426183700562</v>
+        <v>2.89426159858704</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G624" t="n">
-        <v>2.89426183700562</v>
+        <v>2.89426159858704</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G625" t="n">
-        <v>2.85447812080383</v>
+        <v>2.85447835922241</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G630" t="n">
-        <v>2.84453248977661</v>
+        <v>2.84453272819519</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G633" t="n">
-        <v>2.83790183067322</v>
+        <v>2.8379020690918</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G636" t="n">
-        <v>2.72186613082886</v>
+        <v>2.72186589241028</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.70528960227966</v>
+        <v>2.70528984069824</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G641" t="n">
-        <v>2.77822637557983</v>
+        <v>2.77822661399841</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G645" t="n">
-        <v>2.68539810180664</v>
+        <v>2.68539786338806</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G646" t="n">
-        <v>2.73844289779663</v>
+        <v>2.73844265937805</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G648" t="n">
-        <v>2.70197415351868</v>
+        <v>2.7019739151001</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G649" t="n">
-        <v>3.25894546508789</v>
+        <v>3.25894522666931</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G650" t="n">
-        <v>3.29541373252869</v>
+        <v>3.29541397094727</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G652" t="n">
-        <v>3.33519816398621</v>
+        <v>3.33519792556763</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>3.36835026741028</v>
+        <v>3.36835098266602</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G654" t="n">
-        <v>3.36172032356262</v>
+        <v>3.3617205619812</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G655" t="n">
-        <v>3.33519816398621</v>
+        <v>3.33519792556763</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G656" t="n">
-        <v>3.30536031723022</v>
+        <v>3.30536007881165</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.36835026741028</v>
+        <v>3.36835098266602</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G659" t="n">
-        <v>3.22579264640808</v>
+        <v>3.22579216957092</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.75</v>
       </c>
       <c r="G662" t="n">
-        <v>3.1495406627655</v>
+        <v>3.14954042434692</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G663" t="n">
-        <v>3.10312581062317</v>
+        <v>3.10312652587891</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G664" t="n">
-        <v>3.19927024841309</v>
+        <v>3.19927000999451</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G665" t="n">
-        <v>3.12964844703674</v>
+        <v>3.12964868545532</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>3.11638736724854</v>
+        <v>3.11638760566711</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G667" t="n">
-        <v>3.07660412788391</v>
+        <v>3.07660365104675</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.625</v>
       </c>
       <c r="G668" t="n">
-        <v>3.06665778160095</v>
+        <v>3.06665802001953</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G669" t="n">
-        <v>3.05008101463318</v>
+        <v>3.05008149147034</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G672" t="n">
-        <v>3.03350472450256</v>
+        <v>3.03350448608398</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G675" t="n">
-        <v>3.05008101463318</v>
+        <v>3.05008149147034</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G676" t="n">
-        <v>3.05671238899231</v>
+        <v>3.05671167373657</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G679" t="n">
-        <v>2.97714447975159</v>
+        <v>2.97714424133301</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G680" t="n">
-        <v>3.01692819595337</v>
+        <v>3.01692891120911</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.08986496925354</v>
+        <v>3.08986473083496</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>3.05008101463318</v>
+        <v>3.05008149147034</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.05008101463318</v>
+        <v>3.05008149147034</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G684" t="n">
-        <v>3.05008101463318</v>
+        <v>3.05008149147034</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05008101463318</v>
+        <v>3.05008149147034</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G686" t="n">
-        <v>3.11970257759094</v>
+        <v>3.11970281600952</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G687" t="n">
-        <v>3.07660412788391</v>
+        <v>3.07660365104675</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>3.08323454856873</v>
+        <v>3.0832347869873</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G690" t="n">
-        <v>3.04676604270935</v>
+        <v>3.04676556587219</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G691" t="n">
-        <v>3.02024388313293</v>
+        <v>3.0202431678772</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G694" t="n">
-        <v>3.06002712249756</v>
+        <v>3.06002736091614</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G696" t="n">
-        <v>3.02024388313293</v>
+        <v>3.0202431678772</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G697" t="n">
-        <v>3.00698208808899</v>
+        <v>3.00698256492615</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>3.00698208808899</v>
+        <v>3.00698256492615</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G699" t="n">
-        <v>3.01361298561096</v>
+        <v>3.01361274719238</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.375</v>
       </c>
       <c r="G701" t="n">
-        <v>2.90089273452759</v>
+        <v>2.90089249610901</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>2.95725321769714</v>
+        <v>2.95725297927856</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>2.95725321769714</v>
+        <v>2.95725297927856</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>2.89426183700562</v>
+        <v>2.89426159858704</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G709" t="n">
-        <v>2.85116291046143</v>
+        <v>2.85116314888</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G710" t="n">
-        <v>2.81137919425964</v>
+        <v>2.81137943267822</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G711" t="n">
-        <v>2.91083836555481</v>
+        <v>2.91083860397339</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>2.88100051879883</v>
+        <v>2.88100028038025</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>2.86442446708679</v>
+        <v>2.86442470550537</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G716" t="n">
-        <v>2.85447812080383</v>
+        <v>2.85447835922241</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G717" t="n">
-        <v>2.86773920059204</v>
+        <v>2.86773943901062</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G718" t="n">
-        <v>2.83790183067322</v>
+        <v>2.8379020690918</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G719" t="n">
-        <v>2.86442446708679</v>
+        <v>2.86442470550537</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G720" t="n">
-        <v>2.89426183700562</v>
+        <v>2.89426159858704</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>2.85116291046143</v>
+        <v>2.85116314888</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>2.95725321769714</v>
+        <v>2.95725297927856</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G724" t="n">
-        <v>3.03350472450256</v>
+        <v>3.03350448608398</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G725" t="n">
-        <v>3.04345083236694</v>
+        <v>3.0434513092041</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G727" t="n">
-        <v>3.07660412788391</v>
+        <v>3.07660365104675</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G729" t="n">
-        <v>3.00698208808899</v>
+        <v>3.00698256492615</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G730" t="n">
-        <v>3.00035190582275</v>
+        <v>3.00035214424133</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G733" t="n">
-        <v>2.87768530845642</v>
+        <v>2.877685546875</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>2.84784770011902</v>
+        <v>2.8478479385376</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G738" t="n">
-        <v>2.74175810813904</v>
+        <v>2.74175786972046</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G740" t="n">
-        <v>2.69534349441528</v>
+        <v>2.69534373283386</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>2.85116291046143</v>
+        <v>2.85116314888</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>2.84784770011902</v>
+        <v>2.8478479385376</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G747" t="n">
-        <v>2.92078447341919</v>
+        <v>2.92078471183777</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G749" t="n">
-        <v>2.93736100196838</v>
+        <v>2.93736052513123</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>3.05008101463318</v>
+        <v>3.05008149147034</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>2.93736100196838</v>
+        <v>2.93736052513123</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>2.89426183700562</v>
+        <v>2.89426159858704</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G757" t="n">
-        <v>2.79811787605286</v>
+        <v>2.79811763763428</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.125</v>
       </c>
       <c r="G758" t="n">
-        <v>2.73512721061707</v>
+        <v>2.73512744903564</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G760" t="n">
-        <v>2.85447812080383</v>
+        <v>2.85447835922241</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G762" t="n">
-        <v>2.79811787605286</v>
+        <v>2.79811763763428</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G764" t="n">
-        <v>2.82132530212402</v>
+        <v>2.8213255405426</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G766" t="n">
-        <v>2.93736100196838</v>
+        <v>2.93736052513123</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G767" t="n">
-        <v>2.95062208175659</v>
+        <v>2.95062232017517</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>2.92409944534302</v>
+        <v>2.9240996837616</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>2.86773920059204</v>
+        <v>2.86773943901062</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G772" t="n">
-        <v>2.83790183067322</v>
+        <v>2.8379020690918</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G773" t="n">
-        <v>2.84121680259705</v>
+        <v>2.84121656417847</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G775" t="n">
-        <v>2.91415405273438</v>
+        <v>2.9141538143158</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G778" t="n">
-        <v>2.91083836555481</v>
+        <v>2.91083860397339</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G779" t="n">
-        <v>2.91415405273438</v>
+        <v>2.9141538143158</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G780" t="n">
-        <v>2.91083836555481</v>
+        <v>2.91083860397339</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G781" t="n">
-        <v>2.93404603004456</v>
+        <v>2.93404579162598</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>2.93404603004456</v>
+        <v>2.93404579162598</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G783" t="n">
-        <v>2.92078447341919</v>
+        <v>2.92078471183777</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G784" t="n">
-        <v>2.92078447341919</v>
+        <v>2.92078471183777</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>2.95062208175659</v>
+        <v>2.95062232017517</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G786" t="n">
-        <v>2.93736100196838</v>
+        <v>2.93736052513123</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>2.95725321769714</v>
+        <v>2.95725297927856</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G789" t="n">
-        <v>2.96388292312622</v>
+        <v>2.96388339996338</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>2.95393753051758</v>
+        <v>2.953937292099</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G791" t="n">
-        <v>2.93736100196838</v>
+        <v>2.93736052513123</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>3.04345083236694</v>
+        <v>3.0434513092041</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G801" t="n">
-        <v>3.10644149780273</v>
+        <v>3.10644125938416</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G802" t="n">
-        <v>3.1694324016571</v>
+        <v>3.16943264007568</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G803" t="n">
-        <v>3.12964844703674</v>
+        <v>3.12964868545532</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G804" t="n">
-        <v>3.1561713218689</v>
+        <v>3.15617156028748</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G805" t="n">
-        <v>3.17274737358093</v>
+        <v>3.17274785041809</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>3.21584630012512</v>
+        <v>3.21584701538086</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G807" t="n">
-        <v>3.36172032356262</v>
+        <v>3.3617205619812</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>3.35508942604065</v>
+        <v>3.35508918762207</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G809" t="n">
-        <v>3.34845924377441</v>
+        <v>3.34845876693726</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G810" t="n">
-        <v>3.23905396461487</v>
+        <v>3.23905420303345</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.14622497558594</v>
+        <v>3.1462254524231</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.75</v>
       </c>
       <c r="G814" t="n">
-        <v>3.1495406627655</v>
+        <v>3.14954042434692</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>3.1561713218689</v>
+        <v>3.15617156028748</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G817" t="n">
-        <v>3.21916222572327</v>
+        <v>3.21916174888611</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G818" t="n">
-        <v>3.17274737358093</v>
+        <v>3.17274785041809</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G819" t="n">
-        <v>3.14290976524353</v>
+        <v>3.14290952682495</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G821" t="n">
-        <v>3.06002712249756</v>
+        <v>3.06002736091614</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G823" t="n">
-        <v>3.04676604270935</v>
+        <v>3.04676556587219</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>3.01692819595337</v>
+        <v>3.01692891120911</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>3.05339694023132</v>
+        <v>3.05339670181274</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G826" t="n">
-        <v>3.05671238899231</v>
+        <v>3.05671167373657</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G829" t="n">
-        <v>3.12633347511292</v>
+        <v>3.12633371353149</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>3.08323454856873</v>
+        <v>3.0832347869873</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>3.01692819595337</v>
+        <v>3.01692891120911</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>3.07660412788391</v>
+        <v>3.07660365104675</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.11307263374329</v>
+        <v>3.11307215690613</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G839" t="n">
-        <v>3.10312581062317</v>
+        <v>3.10312652587891</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.75</v>
       </c>
       <c r="G840" t="n">
-        <v>3.1495406627655</v>
+        <v>3.14954042434692</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G842" t="n">
-        <v>3.08986496925354</v>
+        <v>3.08986473083496</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.625</v>
       </c>
       <c r="G843" t="n">
-        <v>3.06665778160095</v>
+        <v>3.06665802001953</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.75</v>
       </c>
       <c r="G845" t="n">
-        <v>3.1495406627655</v>
+        <v>3.14954042434692</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G846" t="n">
-        <v>3.11638736724854</v>
+        <v>3.11638760566711</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G847" t="n">
-        <v>3.12633347511292</v>
+        <v>3.12633371353149</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G850" t="n">
-        <v>3.10975742340088</v>
+        <v>3.1097571849823</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G851" t="n">
-        <v>3.09981107711792</v>
+        <v>3.09981060028076</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G852" t="n">
-        <v>3.05339694023132</v>
+        <v>3.05339670181274</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G853" t="n">
-        <v>3.07660412788391</v>
+        <v>3.07660365104675</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G854" t="n">
-        <v>3.10644149780273</v>
+        <v>3.10644125938416</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G855" t="n">
-        <v>3.16280198097229</v>
+        <v>3.16280174255371</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G856" t="n">
-        <v>3.11970257759094</v>
+        <v>3.11970281600952</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G857" t="n">
-        <v>3.09981107711792</v>
+        <v>3.09981060028076</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G858" t="n">
-        <v>3.10312581062317</v>
+        <v>3.10312652587891</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G859" t="n">
-        <v>3.20024681091309</v>
+        <v>3.20024728775024</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>3.16546154022217</v>
+        <v>3.16546201705933</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>3.16546154022217</v>
+        <v>3.16546201705933</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G864" t="n">
-        <v>3.16546154022217</v>
+        <v>3.16546201705933</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>3.1445906162262</v>
+        <v>3.14459037780762</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>3.17241883277893</v>
+        <v>3.17241859436035</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G870" t="n">
-        <v>3.17241883277893</v>
+        <v>3.17241859436035</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G871" t="n">
-        <v>3.25938200950623</v>
+        <v>3.25938153266907</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G872" t="n">
-        <v>3.25938200950623</v>
+        <v>3.25938153266907</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>3.31851696968079</v>
+        <v>3.31851673126221</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>3.33243107795715</v>
+        <v>3.33243060112</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G877" t="n">
-        <v>3.31851696968079</v>
+        <v>3.31851673126221</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>3.31503796577454</v>
+        <v>3.31503844261169</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>3.38460898399353</v>
+        <v>3.38460850715637</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G882" t="n">
-        <v>3.40200185775757</v>
+        <v>3.40200161933899</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G883" t="n">
-        <v>3.43330812454224</v>
+        <v>3.43330836296082</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>3.4472222328186</v>
+        <v>3.44722294807434</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G889" t="n">
-        <v>3.74289774894714</v>
+        <v>3.74289798736572</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G890" t="n">
-        <v>3.74289774894714</v>
+        <v>3.74289798736572</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G892" t="n">
-        <v>3.70811200141907</v>
+        <v>3.70811223983765</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G893" t="n">
-        <v>3.70811200141907</v>
+        <v>3.70811223983765</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.5</v>
       </c>
       <c r="G895" t="n">
-        <v>3.82638168334961</v>
+        <v>3.82638216018677</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>3.85420989990234</v>
+        <v>3.8542103767395</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G897" t="n">
-        <v>3.84029650688171</v>
+        <v>3.84029603004456</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G898" t="n">
-        <v>3.78463983535767</v>
+        <v>3.78464007377625</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G899" t="n">
-        <v>3.72202634811401</v>
+        <v>3.72202610969543</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>3.72202634811401</v>
+        <v>3.72202610969543</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G901" t="n">
-        <v>3.72202634811401</v>
+        <v>3.72202610969543</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73594045639038</v>
+        <v>3.7359402179718</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G903" t="n">
-        <v>3.72898364067078</v>
+        <v>3.7289834022522</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G904" t="n">
-        <v>3.75681114196777</v>
+        <v>3.75681161880493</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G905" t="n">
-        <v>3.75681114196777</v>
+        <v>3.75681161880493</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>3.73594045639038</v>
+        <v>3.7359402179718</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G907" t="n">
-        <v>3.79159641265869</v>
+        <v>3.79159688949585</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5.5</v>
       </c>
       <c r="G908" t="n">
-        <v>3.82638168334961</v>
+        <v>3.82638216018677</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G909" t="n">
-        <v>3.75681114196777</v>
+        <v>3.75681161880493</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G910" t="n">
-        <v>3.6872410774231</v>
+        <v>3.68724131584167</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G911" t="n">
-        <v>3.72202634811401</v>
+        <v>3.72202610969543</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>3.70811200141907</v>
+        <v>3.70811223983765</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G913" t="n">
-        <v>3.67332649230957</v>
+        <v>3.67332696914673</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G914" t="n">
-        <v>3.60375595092773</v>
+        <v>3.60375618934631</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G916" t="n">
-        <v>3.72898364067078</v>
+        <v>3.7289834022522</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G917" t="n">
-        <v>3.68028426170349</v>
+        <v>3.68028354644775</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G919" t="n">
-        <v>3.57592749595642</v>
+        <v>3.57592797279358</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G920" t="n">
-        <v>3.54114294052124</v>
+        <v>3.54114317893982</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>3.54809999465942</v>
+        <v>3.54809975624084</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>3.61767053604126</v>
+        <v>3.61767077445984</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G926" t="n">
-        <v>3.60375595092773</v>
+        <v>3.60375618934631</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G927" t="n">
-        <v>3.57592749595642</v>
+        <v>3.57592797279358</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G928" t="n">
-        <v>3.51331472396851</v>
+        <v>3.51331448554993</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G929" t="n">
-        <v>3.60375595092773</v>
+        <v>3.60375618934631</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>3.54114294052124</v>
+        <v>3.54114317893982</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>3.54809999465942</v>
+        <v>3.54809975624084</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G933" t="n">
-        <v>3.56897163391113</v>
+        <v>3.5689709186554</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>3.51331472396851</v>
+        <v>3.51331448554993</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G935" t="n">
-        <v>3.54114294052124</v>
+        <v>3.54114317893982</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.25</v>
       </c>
       <c r="G937" t="n">
-        <v>3.65245628356934</v>
+        <v>3.6524555683136</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G938" t="n">
-        <v>3.6872410774231</v>
+        <v>3.68724131584167</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G940" t="n">
-        <v>3.63854169845581</v>
+        <v>3.63854098320007</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G941" t="n">
-        <v>3.72898364067078</v>
+        <v>3.7289834022522</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>3.68028426170349</v>
+        <v>3.68028354644775</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G944" t="n">
-        <v>3.70811200141907</v>
+        <v>3.70811223983765</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>3.74289774894714</v>
+        <v>3.74289798736572</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>3.70811200141907</v>
+        <v>3.70811223983765</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G947" t="n">
-        <v>3.6872410774231</v>
+        <v>3.68724131584167</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G948" t="n">
-        <v>3.70115518569946</v>
+        <v>3.70115566253662</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>3.66636943817139</v>
+        <v>3.66636991500854</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>5.25</v>
       </c>
       <c r="G951" t="n">
-        <v>3.65245628356934</v>
+        <v>3.6524555683136</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G952" t="n">
-        <v>3.66636943817139</v>
+        <v>3.66636991500854</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>3.70811200141907</v>
+        <v>3.70811223983765</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G954" t="n">
-        <v>3.72202634811401</v>
+        <v>3.72202610969543</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G955" t="n">
-        <v>3.73594045639038</v>
+        <v>3.7359402179718</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G956" t="n">
-        <v>3.72202634811401</v>
+        <v>3.72202610969543</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G957" t="n">
-        <v>3.73594045639038</v>
+        <v>3.7359402179718</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G959" t="n">
-        <v>3.79855442047119</v>
+        <v>3.79855394363403</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>3.72202634811401</v>
+        <v>3.72202610969543</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G962" t="n">
-        <v>3.6872410774231</v>
+        <v>3.68724131584167</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>3.79159641265869</v>
+        <v>3.79159688949585</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>5.5</v>
       </c>
       <c r="G964" t="n">
-        <v>3.82638168334961</v>
+        <v>3.82638216018677</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>3.75681114196777</v>
+        <v>3.75681161880493</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G966" t="n">
-        <v>3.79159641265869</v>
+        <v>3.79159688949585</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.5</v>
       </c>
       <c r="G967" t="n">
-        <v>3.82638168334961</v>
+        <v>3.82638216018677</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>3.79855442047119</v>
+        <v>3.79855394363403</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G969" t="n">
-        <v>3.8055112361908</v>
+        <v>3.80551028251648</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G970" t="n">
-        <v>3.83333969116211</v>
+        <v>3.83333921432495</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G971" t="n">
-        <v>3.81942510604858</v>
+        <v>3.81942462921143</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G972" t="n">
-        <v>3.84029650688171</v>
+        <v>3.84029603004456</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>3.84029650688171</v>
+        <v>3.84029603004456</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>3.86116790771484</v>
+        <v>3.86116743087769</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G975" t="n">
-        <v>3.83333969116211</v>
+        <v>3.83333921432495</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G979" t="n">
-        <v>4.03509378433228</v>
+        <v>4.03509426116943</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G980" t="n">
-        <v>4.01422262191772</v>
+        <v>4.01422214508057</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G983" t="n">
-        <v>3.888995885849</v>
+        <v>3.88899564743042</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G984" t="n">
-        <v>3.96552276611328</v>
+        <v>3.96552324295044</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G987" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G989" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G990" t="n">
-        <v>4.11857843399048</v>
+        <v>4.11857891082764</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>4.06292200088501</v>
+        <v>4.06292247772217</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G993" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G994" t="n">
-        <v>4.14640617370605</v>
+        <v>4.14640665054321</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G995" t="n">
-        <v>4.1533637046814</v>
+        <v>4.15336322784424</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G996" t="n">
-        <v>4.20902061462402</v>
+        <v>4.20902013778687</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G997" t="n">
-        <v>4.27163314819336</v>
+        <v>4.27163410186768</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G998" t="n">
-        <v>4.24380493164062</v>
+        <v>4.24380540847778</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.29946231842041</v>
+        <v>4.29946279525757</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.33424758911133</v>
+        <v>4.33424711227417</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.25771999359131</v>
+        <v>4.25771951675415</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.25076293945312</v>
+        <v>4.25076246261597</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.38990354537964</v>
+        <v>4.3899040222168</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.35511827468872</v>
+        <v>4.35511875152588</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.25</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.3481616973877</v>
+        <v>4.34816122055054</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.32033348083496</v>
+        <v>4.3203330039978</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.31337594985962</v>
+        <v>4.31337642669678</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.31337594985962</v>
+        <v>4.31337642669678</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.20206308364868</v>
+        <v>4.20206356048584</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.1533637046814</v>
+        <v>4.15336322784424</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.19510698318481</v>
+        <v>4.19510650634766</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.18814945220947</v>
+        <v>4.18814897537231</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.21597719192505</v>
+        <v>4.21597766876221</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>6</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.17423439025879</v>
+        <v>4.17423534393311</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>6</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.17423439025879</v>
+        <v>4.17423534393311</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.1533637046814</v>
+        <v>4.15336322784424</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>6</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.17423439025879</v>
+        <v>4.17423534393311</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>6</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.17423439025879</v>
+        <v>4.17423534393311</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.19510698318481</v>
+        <v>4.19510650634766</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.20902061462402</v>
+        <v>4.20902013778687</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.17423439025879</v>
+        <v>4.17423534393311</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.19510698318481</v>
+        <v>4.19510650634766</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.13249254226685</v>
+        <v>4.132493019104</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.10466432571411</v>
+        <v>4.10466480255127</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.13249254226685</v>
+        <v>4.132493019104</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.07683610916138</v>
+        <v>4.07683658599854</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.07683610916138</v>
+        <v>4.07683658599854</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.97248029708862</v>
+        <v>3.97247982025146</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.13249254226685</v>
+        <v>4.132493019104</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.25076293945312</v>
+        <v>4.25076246261597</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.22989177703857</v>
+        <v>4.22989225387573</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.91682314872742</v>
+        <v>3.91682362556458</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.95160889625549</v>
+        <v>3.95160937309265</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.81942510604858</v>
+        <v>3.81942462921143</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.78463983535767</v>
+        <v>3.78464007377625</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.6872410774231</v>
+        <v>3.68724131584167</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.70811200141907</v>
+        <v>3.70811223983765</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.74289774894714</v>
+        <v>3.74289798736572</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.74289774894714</v>
+        <v>3.74289798736572</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.63158416748047</v>
+        <v>3.63158464431763</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.41939425468445</v>
+        <v>3.41939353942871</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.36721611022949</v>
+        <v>3.36721658706665</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.82456564903259</v>
+        <v>2.82456588745117</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.90109324455261</v>
+        <v>2.90109348297119</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.03675603866577</v>
+        <v>3.03675556182861</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.89413642883301</v>
+        <v>2.89413619041443</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.1758975982666</v>
+        <v>3.17589735984802</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>4.75</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.304603099823</v>
+        <v>3.30460262298584</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.41939425468445</v>
+        <v>3.41939353942871</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.304603099823</v>
+        <v>3.30460262298584</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.4715723991394</v>
+        <v>3.47157216072083</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.875</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.39156603813171</v>
+        <v>3.39156627655029</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.49940085411072</v>
+        <v>3.49940061569214</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.47852921485901</v>
+        <v>3.47852897644043</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.56897163391113</v>
+        <v>3.5689709186554</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.56897163391113</v>
+        <v>3.5689709186554</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.58288526535034</v>
+        <v>3.58288502693176</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>5</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.47852921485901</v>
+        <v>3.47852897644043</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.50635719299316</v>
+        <v>3.50635766983032</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.51331472396851</v>
+        <v>3.51331448554993</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.54809999465942</v>
+        <v>3.54809975624084</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.51331472396851</v>
+        <v>3.51331448554993</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.41591548919678</v>
+        <v>3.41591596603394</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>4.75</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.304603099823</v>
+        <v>3.30460262298584</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>4.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.304603099823</v>
+        <v>3.30460262298584</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.46461486816406</v>
+        <v>3.46461510658264</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.56897163391113</v>
+        <v>3.5689709186554</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.70115518569946</v>
+        <v>3.70115566253662</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.55505681037903</v>
+        <v>3.55505657196045</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.61071348190308</v>
+        <v>3.6107132434845</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.61767053604126</v>
+        <v>3.61767077445984</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.54809999465942</v>
+        <v>3.54809975624084</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.69419836997986</v>
+        <v>3.69419813156128</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.63854169845581</v>
+        <v>3.63854098320007</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.70115518569946</v>
+        <v>3.70115566253662</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.61767053604126</v>
+        <v>3.61767077445984</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.61767053604126</v>
+        <v>3.61767077445984</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.56897163391113</v>
+        <v>3.5689709186554</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.79855442047119</v>
+        <v>3.79855394363403</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.91682314872742</v>
+        <v>3.91682362556458</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.93073844909668</v>
+        <v>3.93073797225952</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.95160889625549</v>
+        <v>3.95160937309265</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>5.75</v>
       </c>
       <c r="G1126" t="n">
-        <v>4.00030899047852</v>
+        <v>4.0003080368042</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.888995885849</v>
+        <v>3.88899564743042</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.92378044128418</v>
+        <v>3.92378091812134</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1131" t="n">
-        <v>4.04900789260864</v>
+        <v>4.0490083694458</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1132" t="n">
-        <v>4.02117967605591</v>
+        <v>4.02118015289307</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93073844909668</v>
+        <v>3.93073797225952</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1136" t="n">
-        <v>4.11857843399048</v>
+        <v>4.11857891082764</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1137" t="n">
-        <v>4.02813720703125</v>
+        <v>4.02813673019409</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.03509378433228</v>
+        <v>4.03509426116943</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.04205131530762</v>
+        <v>4.04205083847046</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.75</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.00030899047852</v>
+        <v>4.0003080368042</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1146" t="n">
-        <v>4.06987953186035</v>
+        <v>4.06987905502319</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>5.75</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.00030899047852</v>
+        <v>4.0003080368042</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.93073844909668</v>
+        <v>3.93073797225952</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.75</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.00030899047852</v>
+        <v>4.0003080368042</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.09770774841309</v>
+        <v>4.09770727157593</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.04900789260864</v>
+        <v>4.0490083694458</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.10466432571411</v>
+        <v>4.10466480255127</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1156" t="n">
-        <v>4.10466432571411</v>
+        <v>4.10466480255127</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1157" t="n">
-        <v>4.10466432571411</v>
+        <v>4.10466480255127</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.10466432571411</v>
+        <v>4.10466480255127</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1159" t="n">
-        <v>4.09770774841309</v>
+        <v>4.09770727157593</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.04186010360718</v>
+        <v>4.04186058044434</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.97666907310486</v>
+        <v>3.9766685962677</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1164" t="n">
-        <v>4.03461647033691</v>
+        <v>4.03461742401123</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>5.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.98391246795654</v>
+        <v>3.98391199111938</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.96942543983459</v>
+        <v>3.96942496299744</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.9476945400238</v>
+        <v>3.94769549369812</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.9476945400238</v>
+        <v>3.94769549369812</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.92596459388733</v>
+        <v>3.92596507072449</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.9476945400238</v>
+        <v>3.94769549369812</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.96942543983459</v>
+        <v>3.96942496299744</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.96942543983459</v>
+        <v>3.96942496299744</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.92596459388733</v>
+        <v>3.92596507072449</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.96942543983459</v>
+        <v>3.96942496299744</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.9476945400238</v>
+        <v>3.94769549369812</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.92596459388733</v>
+        <v>3.92596507072449</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.92596459388733</v>
+        <v>3.92596507072449</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.04186010360718</v>
+        <v>4.04186058044434</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.3533296585083</v>
+        <v>4.35333013534546</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>6</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.34608602523804</v>
+        <v>4.3460865020752</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.14326858520508</v>
+        <v>4.14326810836792</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.9042341709137</v>
+        <v>3.90423369407654</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.8752601146698</v>
+        <v>3.87525987625122</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>5.5</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.98391246795654</v>
+        <v>3.98391199111938</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.92596459388733</v>
+        <v>3.92596507072449</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1210" t="n">
-        <v>4.04910373687744</v>
+        <v>4.04910326004028</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.99839949607849</v>
+        <v>3.99839901924133</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.97666907310486</v>
+        <v>3.9766685962677</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.88974714279175</v>
+        <v>3.88974666595459</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.88250422477722</v>
+        <v>3.88250374794006</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.94045114517212</v>
+        <v>3.94045209884644</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.9042341709137</v>
+        <v>3.90423369407654</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.92596459388733</v>
+        <v>3.92596507072449</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.97666907310486</v>
+        <v>3.9766685962677</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.04910373687744</v>
+        <v>4.04910326004028</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.92596459388733</v>
+        <v>3.92596507072449</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.88250422477722</v>
+        <v>3.88250374794006</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.94045114517212</v>
+        <v>3.94045209884644</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1234" t="n">
-        <v>4.04910373687744</v>
+        <v>4.04910326004028</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.04186010360718</v>
+        <v>4.04186058044434</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.04910373687744</v>
+        <v>4.04910326004028</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.04186010360718</v>
+        <v>4.04186058044434</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.94045114517212</v>
+        <v>3.94045209884644</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.9042341709137</v>
+        <v>3.90423369407654</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.94045114517212</v>
+        <v>3.94045209884644</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.9042341709137</v>
+        <v>3.90423369407654</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.88974714279175</v>
+        <v>3.88974666595459</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.94045114517212</v>
+        <v>3.94045209884644</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.88250422477722</v>
+        <v>3.88250374794006</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.86801719665527</v>
+        <v>3.86801671981812</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.9042341709137</v>
+        <v>3.90423369407654</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>5.25</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.80282545089722</v>
+        <v>3.80282592773438</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.85353064537048</v>
+        <v>3.85353016853333</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.96942543983459</v>
+        <v>3.96942496299744</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1261" t="n">
-        <v>3.94045114517212</v>
+        <v>3.94045209884644</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>5.5</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.98391246795654</v>
+        <v>3.98391199111938</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.9476945400238</v>
+        <v>3.94769549369812</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>3.9476945400238</v>
+        <v>3.94769549369812</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1273" t="n">
-        <v>3.9042341709137</v>
+        <v>3.90423369407654</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1274" t="n">
-        <v>3.8752601146698</v>
+        <v>3.87525987625122</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.8752601146698</v>
+        <v>3.87525987625122</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.86801719665527</v>
+        <v>3.86801671981812</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.81731224060059</v>
+        <v>3.81731271743774</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.25</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.80282545089722</v>
+        <v>3.80282592773438</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.8100688457489</v>
+        <v>3.81006932258606</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>5.25</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.80282545089722</v>
+        <v>3.80282592773438</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.73039031028748</v>
+        <v>3.73039054870605</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.73039031028748</v>
+        <v>3.73039054870605</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.73039031028748</v>
+        <v>3.73039054870605</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.69417309761047</v>
+        <v>3.69417262077332</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.69417309761047</v>
+        <v>3.69417262077332</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.75212097167969</v>
+        <v>3.75212121009827</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.77385139465332</v>
+        <v>3.77385187149048</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.81731224060059</v>
+        <v>3.81731271743774</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.77385139465332</v>
+        <v>3.77385187149048</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.85353064537048</v>
+        <v>3.85353016853333</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.57103443145752</v>
+        <v>3.57103395462036</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.81500005722046</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.48773407936096</v>
+        <v>3.48773455619812</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.40805625915527</v>
+        <v>3.40805602073669</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.43703007698059</v>
+        <v>3.43702983856201</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.36459541320801</v>
+        <v>3.36459517478943</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.29940366744995</v>
+        <v>3.29940342903137</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.3319993019104</v>
+        <v>3.33199954032898</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.26680850982666</v>
+        <v>3.26680827140808</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.26680850982666</v>
+        <v>3.26680827140808</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.23783397674561</v>
+        <v>3.23783445358276</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.39356875419617</v>
+        <v>3.39356899261475</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.36097359657288</v>
+        <v>3.36097311973572</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.625</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.35010814666748</v>
+        <v>3.35010838508606</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.48411250114441</v>
+        <v>3.48411273956299</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.46600341796875</v>
+        <v>3.46600389480591</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.48411250114441</v>
+        <v>3.48411273956299</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.48049068450928</v>
+        <v>3.4804904460907</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.51308631896973</v>
+        <v>3.51308679580688</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.55654740333557</v>
+        <v>3.55654692649841</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.75</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.44065165519714</v>
+        <v>3.44065141677856</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.4768693447113</v>
+        <v>3.47686910629272</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.48411250114441</v>
+        <v>3.48411273956299</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.48411250114441</v>
+        <v>3.48411273956299</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.44065165519714</v>
+        <v>3.44065141677856</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.65795588493347</v>
+        <v>3.65795636177063</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.60363030433655</v>
+        <v>3.60362982749939</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.5456817150116</v>
+        <v>3.54568219184875</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.53843855857849</v>
+        <v>3.53843879699707</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.56016874313354</v>
+        <v>3.56016898155212</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.55654740333557</v>
+        <v>3.55654692649841</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.60363030433655</v>
+        <v>3.60362982749939</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.68692994117737</v>
+        <v>3.68693041801453</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.65795588493347</v>
+        <v>3.65795636177063</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.69417309761047</v>
+        <v>3.69417262077332</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.68692994117737</v>
+        <v>3.68693041801453</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.61449480056763</v>
+        <v>3.61449503898621</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.65795588493347</v>
+        <v>3.65795636177063</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.75184750556946</v>
+        <v>3.7518470287323</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.96091675758362</v>
+        <v>3.96091723442078</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.96091675758362</v>
+        <v>3.96091723442078</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.97612190246582</v>
+        <v>3.97612142562866</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.86968636512756</v>
+        <v>3.86968684196472</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.87728881835938</v>
+        <v>3.87728834152222</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.86208367347717</v>
+        <v>3.86208415031433</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.87728881835938</v>
+        <v>3.87728834152222</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.86208367347717</v>
+        <v>3.86208415031433</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.7670521736145</v>
+        <v>3.76705265045166</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.75184750556946</v>
+        <v>3.7518470287323</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.77085328102112</v>
+        <v>3.77085375785828</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.75184750556946</v>
+        <v>3.7518470287323</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.86208367347717</v>
+        <v>3.86208415031433</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.86968636512756</v>
+        <v>3.86968684196472</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.86968636512756</v>
+        <v>3.86968684196472</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.86968636512756</v>
+        <v>3.86968684196472</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.07495498657227</v>
+        <v>4.07495450973511</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.86968636512756</v>
+        <v>3.86968684196472</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.86968636512756</v>
+        <v>3.86968684196472</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.96091675758362</v>
+        <v>3.96091723442078</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.97612190246582</v>
+        <v>3.97612142562866</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.97612190246582</v>
+        <v>3.97612142562866</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1472" t="n">
-        <v>4.07495498657227</v>
+        <v>4.07495450973511</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1478" t="n">
-        <v>4.17378759384155</v>
+        <v>4.17378711700439</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.07495498657227</v>
+        <v>4.07495450973511</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.97612190246582</v>
+        <v>3.97612142562866</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.87728881835938</v>
+        <v>3.87728834152222</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.86208367347717</v>
+        <v>3.86208415031433</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.86208367347717</v>
+        <v>3.86208415031433</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.86968636512756</v>
+        <v>3.86968684196472</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.96091675758362</v>
+        <v>3.96091723442078</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.90009665489197</v>
+        <v>3.90009617805481</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.96091675758362</v>
+        <v>3.96091723442078</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.97612190246582</v>
+        <v>3.97612142562866</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.96091675758362</v>
+        <v>3.96091723442078</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.96091675758362</v>
+        <v>3.96091723442078</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.07495498657227</v>
+        <v>4.07495450973511</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1585" t="n">
-        <v>4.33343982696533</v>
+        <v>4.33344030380249</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1586" t="n">
-        <v>4.34864521026611</v>
+        <v>4.34864473342896</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.34864521026611</v>
+        <v>4.34864473342896</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.34864521026611</v>
+        <v>4.34864473342896</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1598" t="n">
-        <v>4.272620677948</v>
+        <v>4.27262020111084</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.272620677948</v>
+        <v>4.27262020111084</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G1611" t="n">
-        <v>4.32963895797729</v>
+        <v>4.32963943481445</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G1613" t="n">
-        <v>4.29922962188721</v>
+        <v>4.29922914505005</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1615" t="n">
-        <v>4.22320413589478</v>
+        <v>4.22320365905762</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1616" t="n">
-        <v>4.24220991134644</v>
+        <v>4.24221038818359</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.33343982696533</v>
+        <v>4.33344030380249</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>4.38000011444092</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>176563</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>4.40500020980835</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>4.36499977111816</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>4.36999988555908</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>4.34999990463257</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>4.31500005722046</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>379727</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>4.34499979019165</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>4.32999992370605</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>4.30499982833862</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>457873</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>4.34999990463257</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>4.23999977111816</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>412699</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>4.2649998664856</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>4.17500019073486</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>4.25500011444092</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>4.25500011444092</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>4.19000005722046</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>332755</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>4.19000005722046</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>4.21000003814697</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RWAY.MI.xlsx
+++ b/data/RWAY.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>316290</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>4.26999998092651</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>4.20499992370605</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>4.22499990463257</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>4.22499990463257</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
